--- a/sheets/민요/검수/잦은 뱃노리.xlsx
+++ b/sheets/민요/검수/잦은 뱃노리.xlsx
@@ -4,15 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -21,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -51,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -74,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +176,66 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5961,8 +6100,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U28"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -5985,1540 +6128,1633 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잦은 뱃노리 — 민요채보-3/잦은 뱃노리.png (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">잦은 뱃노리</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I3" s="20"/>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="M3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="R3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="S3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="T3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="U3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="21"/>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M4" s="21"/>
+      <c r="N4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="O4" s="21"/>
+      <c r="P4" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="S4" s="21"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="21"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="22"/>
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="E5" s="22"/>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="L5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O5" s="22"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="S5" s="22"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="22"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="G6" s="20"/>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I6" s="20"/>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M6" s="20"/>
+      <c r="N6" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O6" s="20"/>
+      <c r="P6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="Q6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="R6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C7" s="21"/>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="G7" s="21"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K7" s="21"/>
+      <c r="L7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M7" s="21"/>
+      <c r="N7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O7" s="21"/>
+      <c r="P7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="R7" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="T7" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E8" s="22"/>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G8" s="22"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K8" s="22"/>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ‹</t>
-        </is>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △
 ‹</t>
-        </is>
-      </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O8" s="22"/>
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="Q8" s="22"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="22"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">뱃</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="R9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="S9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="T9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="U9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="21"/>
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="21"/>
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="K10" s="21"/>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="M10" s="21"/>
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="P10" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="S10" s="21"/>
+      <c r="T10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="U10" s="21"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="22"/>
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="22"/>
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">넘</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="22"/>
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="22"/>
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="22"/>
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="22"/>
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="Q11" s="22"/>
+      <c r="R11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="S11" s="22"/>
+      <c r="T11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="U11" s="22"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="N12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="R12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="S12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="T12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="U12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="C13" s="21"/>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E13" s="21"/>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G13" s="21"/>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I13" s="21"/>
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="K13" s="21"/>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M13" s="21"/>
+      <c r="N13" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O13" s="21"/>
+      <c r="P13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="Q13" s="21"/>
+      <c r="R13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S13" s="21"/>
+      <c r="T13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U13" s="21"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="C14" s="22"/>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E14" s="22"/>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ‹</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="I14" s="22"/>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K14" s="22"/>
+      <c r="L14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="M14" s="22"/>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ○</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O14" s="22"/>
+      <c r="P14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙</t>
         </is>
       </c>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="U14" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잦은 뱃노리 — 민요채보-3/잦은 뱃노리.png (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="Q14" s="23"/>
+      <c r="R14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S14" s="22"/>
+      <c r="T14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U14" s="22"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">잦은 뱃노리</t>
+        </is>
+      </c>
+      <c s="8" r="C16"/>
+      <c s="8" r="D16"/>
+      <c s="8" r="E16"/>
+      <c s="8" r="F16"/>
+      <c s="8" r="G16"/>
+      <c s="8" r="H16"/>
+      <c s="8" r="I16"/>
+      <c s="8" r="J16"/>
+      <c s="8" r="K16"/>
+      <c s="8" r="L16"/>
+      <c s="8" r="M16"/>
+      <c s="8" r="N16"/>
+      <c s="8" r="O16"/>
+      <c s="8" r="P16"/>
+      <c s="8" r="Q16"/>
+      <c s="8" r="R16"/>
+      <c s="8" r="S16"/>
+      <c s="8" r="T16"/>
+      <c s="8" r="U16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="19"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="S17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="T17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="U17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">교</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="19"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="Q18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="R18" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="S18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="T18" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="U18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">향</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="19"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="Q19" s="22"/>
+      <c r="R19" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="S19" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="T19" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="U19" s="22"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="B20" s="19"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="Q20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="R20" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="S20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="T20" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="U20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="19"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="Q21" s="21"/>
+      <c r="R21" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="S21" s="21"/>
+      <c r="T21" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U21" s="21"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="B22" s="19"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S22" s="22"/>
+      <c r="T22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U22" s="22"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="B23" s="19"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="Q23" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="R23" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="S23" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="T23" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="U23" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="24" ht="56" customHeight="1">
+      <c r="B24" s="19"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="Q24" s="21"/>
+      <c r="R24" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="S24" s="21"/>
+      <c r="T24" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="U24" s="21"/>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="B25" s="19"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="Q25" s="22"/>
+      <c r="R25" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="S25" s="22"/>
+      <c r="T25" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="U25" s="22"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="B26" s="19"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="Q26" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="R26" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="S26" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="T26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="U26" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+    <row r="27" ht="56" customHeight="1">
+      <c r="B27" s="19"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="S27" s="21"/>
+      <c r="T27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U27" s="21"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="B28" s="19"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="Q28" s="22"/>
+      <c r="R28" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="S28" s="22"/>
+      <c r="T28" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
+      <c r="U28" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B16:U16"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="14" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/잦은 뱃노리.xlsx
+++ b/sheets/민요/검수/잦은 뱃노리.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -619,12 +619,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="2"/>
@@ -794,12 +794,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I17" s="2"/>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I20" s="2"/>
@@ -1773,7 +1773,7 @@
       <c r="E5" s="10"/>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G5" s="10"/>
@@ -1785,13 +1785,13 @@
       <c r="I5" s="10"/>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="10"/>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="10"/>
@@ -1971,7 +1971,7 @@
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="9"/>

--- a/sheets/민요/검수/잦은 뱃노리.xlsx
+++ b/sheets/민요/검수/잦은 뱃노리.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1674,330 +1703,330 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">잦은 뱃노리</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="E3" s="22"/>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="G3" s="22"/>
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無無無</t>
         </is>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="I3" s="22"/>
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="K3" s="22"/>
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="M3" s="8"/>
+      <c r="M3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E4" s="23"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="G4" s="23"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰潢汰無汰</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="K4" s="23"/>
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
+      <c r="M4" s="23"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="B5" s="21"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="24"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△無無無</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="24"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="24"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
+      <c r="M5" s="24"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="8"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="9"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I7" s="23"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰無汰</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="C8" s="24"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G8" s="24"/>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I8" s="24"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢太</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="10"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="24"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢太</t>
         </is>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="E9" s="22"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="8"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G10" s="23"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢太汰無汰</t>
         </is>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="9"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="23"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="10"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰無汰</t>
         </is>
       </c>
-      <c r="M12" s="8"/>
+      <c r="M12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="B13" s="21"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="9"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="B14" s="21"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">‹</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
+      <c r="M14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/잦은 뱃노리.xlsx
+++ b/sheets/민요/검수/잦은 뱃노리.xlsx
@@ -1684,24 +1684,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -1844,7 +1844,7 @@
       <c r="L6" s="21"/>
       <c r="M6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
       <c r="L7" s="21"/>
       <c r="M7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
       <c r="L8" s="21"/>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -1925,7 +1925,7 @@
       <c r="L9" s="21"/>
       <c r="M9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
       <c r="L10" s="21"/>
       <c r="M10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -1971,7 +1971,7 @@
       <c r="L11" s="21"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="M12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -2009,7 +2009,7 @@
       <c r="L13" s="21"/>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>

--- a/sheets/민요/검수/잦은 뱃노리.xlsx
+++ b/sheets/민요/검수/잦은 뱃노리.xlsx
@@ -718,12 +718,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I6" s="2"/>
@@ -2023,7 +2023,7 @@
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M14" s="24"/>

--- a/sheets/민요/검수/잦은 뱃노리.xlsx
+++ b/sheets/민요/검수/잦은 뱃노리.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -222,6 +227,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1727,37 +1741,37 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="25"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E3" s="22"/>
+      <c r="E3" s="25"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="25"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無無無</t>
         </is>
       </c>
-      <c r="I3" s="22"/>
+      <c r="I3" s="25"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="K3" s="22"/>
+      <c r="K3" s="25"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="M3" s="22"/>
+      <c r="M3" s="25"/>
     </row>
     <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
@@ -1766,83 +1780,83 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C4" s="23"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="26"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="26"/>
       <c r="H4" s="21"/>
-      <c r="I4" s="23"/>
+      <c r="I4" s="26"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰潢汰無汰</t>
         </is>
       </c>
-      <c r="K4" s="23"/>
+      <c r="K4" s="26"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰</t>
         </is>
       </c>
-      <c r="M4" s="23"/>
+      <c r="M4" s="26"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="24"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="21"/>
-      <c r="E5" s="24"/>
+      <c r="E5" s="27"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="24"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△無無無</t>
         </is>
       </c>
-      <c r="I5" s="24"/>
+      <c r="I5" s="27"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="24"/>
+      <c r="K5" s="27"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="24"/>
+      <c r="M5" s="27"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="21"/>
-      <c r="G6" s="22"/>
+      <c r="G6" s="25"/>
       <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
+      <c r="I6" s="25"/>
       <c r="J6" s="21"/>
-      <c r="K6" s="22"/>
+      <c r="K6" s="25"/>
       <c r="L6" s="21"/>
-      <c r="M6" s="22"/>
+      <c r="M6" s="25"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -1851,21 +1865,21 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="23"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="21"/>
-      <c r="G7" s="23"/>
+      <c r="G7" s="26"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I7" s="23"/>
+      <c r="I7" s="26"/>
       <c r="J7" s="21"/>
-      <c r="K7" s="23"/>
+      <c r="K7" s="26"/>
       <c r="L7" s="21"/>
-      <c r="M7" s="23"/>
+      <c r="M7" s="26"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -1874,56 +1888,56 @@
           <t xml:space="preserve">潢汰無汰</t>
         </is>
       </c>
-      <c r="C8" s="24"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E8" s="24"/>
+      <c r="E8" s="27"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G8" s="24"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I8" s="24"/>
+      <c r="I8" s="27"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢太</t>
         </is>
       </c>
-      <c r="K8" s="24"/>
+      <c r="K8" s="27"/>
       <c r="L8" s="21"/>
-      <c r="M8" s="24"/>
+      <c r="M8" s="27"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢太</t>
         </is>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="21"/>
-      <c r="G9" s="22"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="25"/>
       <c r="J9" s="21"/>
-      <c r="K9" s="22"/>
+      <c r="K9" s="25"/>
       <c r="L9" s="21"/>
-      <c r="M9" s="22"/>
+      <c r="M9" s="25"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
@@ -1932,101 +1946,101 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="23"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="21"/>
-      <c r="E10" s="23"/>
+      <c r="E10" s="26"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G10" s="23"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="21"/>
-      <c r="I10" s="23"/>
+      <c r="I10" s="26"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢太汰無汰</t>
         </is>
       </c>
-      <c r="K10" s="23"/>
+      <c r="K10" s="26"/>
       <c r="L10" s="21"/>
-      <c r="M10" s="23"/>
+      <c r="M10" s="26"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="24"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="24"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="21"/>
-      <c r="G11" s="24"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="21"/>
-      <c r="I11" s="24"/>
+      <c r="I11" s="27"/>
       <c r="J11" s="21"/>
-      <c r="K11" s="24"/>
+      <c r="K11" s="27"/>
       <c r="L11" s="21"/>
-      <c r="M11" s="24"/>
+      <c r="M11" s="27"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
-      <c r="C12" s="22"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="21"/>
-      <c r="E12" s="22"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="21"/>
-      <c r="G12" s="22"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="21"/>
-      <c r="I12" s="22"/>
+      <c r="I12" s="25"/>
       <c r="J12" s="21"/>
-      <c r="K12" s="22"/>
+      <c r="K12" s="25"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰無汰</t>
         </is>
       </c>
-      <c r="M12" s="22"/>
+      <c r="M12" s="25"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
+      <c r="C13" s="26"/>
       <c r="D13" s="21"/>
-      <c r="E13" s="23"/>
+      <c r="E13" s="26"/>
       <c r="F13" s="21"/>
-      <c r="G13" s="23"/>
+      <c r="G13" s="26"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="26"/>
       <c r="J13" s="21"/>
-      <c r="K13" s="23"/>
+      <c r="K13" s="26"/>
       <c r="L13" s="21"/>
-      <c r="M13" s="23"/>
+      <c r="M13" s="26"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
-      <c r="C14" s="24"/>
+      <c r="C14" s="27"/>
       <c r="D14" s="21"/>
-      <c r="E14" s="24"/>
+      <c r="E14" s="27"/>
       <c r="F14" s="21"/>
-      <c r="G14" s="24"/>
+      <c r="G14" s="27"/>
       <c r="H14" s="21"/>
-      <c r="I14" s="24"/>
+      <c r="I14" s="27"/>
       <c r="J14" s="21"/>
-      <c r="K14" s="24"/>
+      <c r="K14" s="27"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M14" s="24"/>
+      <c r="M14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/잦은 뱃노리.xlsx
+++ b/sheets/민요/검수/잦은 뱃노리.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,19 +218,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -308,7 +306,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4 / 12정간</t>
+          <t xml:space="preserve">4/4 / 16정간</t>
         </is>
       </c>
     </row>
@@ -332,7 +330,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">132</t>
         </is>
       </c>
     </row>
@@ -344,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
     </row>
@@ -368,7 +366,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">상</t>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
     </row>
@@ -378,7 +376,11 @@
           <t xml:space="preserve">확인 필요</t>
         </is>
       </c>
-      <c r="B12" s="4"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 17%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0"/>
@@ -404,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12정간. 머리 "잦은 뱃노리 &lt;자즌물이&gt; 후렴", "3번". 손글씨 흘림·겹침 심해 다수 칸 추정(㳞=청중, 汰=청태, 潢=청황). 율명·기호 위주 전사, 가사 칸(각 율명열 오른쪽)은 사용자가 채우도록 비워 둠. 박자/행수는 12정간 굿거리형으로 봄. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 선 4칸마다) → 4/4·16. 오른쪽 끝 빈 줄 1개 제외하고 9줄. 머리 "잦은 뱃노래 &lt;자즌몰이&gt; 후렴", "3번". 古 모양 글자는 南 흘림으로 봄(仲·南·無 진행). 줄3 12정간 아래 굵은 덧줄, 줄2·6 일부 동그라미 묶음(생략). 한 곡.</t>
         </is>
       </c>
     </row>
@@ -590,18 +592,27 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="4"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^|–無</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^
+–無</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어야</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無 오른쪽 작은 ▾ 꾸밈</t>
+        </is>
+      </c>
       <c r="K2" s="2"/>
     </row>
     <row r="3">
@@ -627,15 +638,20 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰</t>
+          <t xml:space="preserve">無|–無</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰</t>
-        </is>
-      </c>
-      <c r="I3" s="2"/>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디야</t>
+        </is>
+      </c>
       <c r="J3" s="4"/>
       <c r="K3" s="2"/>
     </row>
@@ -690,19 +706,20 @@
         <v>1</v>
       </c>
       <c r="E5" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰無汰</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰無汰</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I5" s="2"/>
@@ -725,23 +742,33 @@
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>4</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|汰|黃</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+汰
+黃</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어기야</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세 번째 글자 氵 안 보임(潢일 수도)</t>
+        </is>
+      </c>
       <c r="K6" s="2"/>
     </row>
     <row r="7">
@@ -754,28 +781,33 @@
         </is>
       </c>
       <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="2">
-        <v>2</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無汰</t>
+          <t xml:space="preserve">無|–無</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無汰</t>
-        </is>
-      </c>
-      <c r="I7" s="2"/>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디야</t>
+        </is>
+      </c>
       <c r="J7" s="4"/>
       <c r="K7" s="2"/>
     </row>
@@ -789,25 +821,25 @@
         </is>
       </c>
       <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2">
         <v>2</v>
       </c>
-      <c r="D8" s="2">
-        <v>2</v>
-      </c>
-      <c r="E8" s="2">
-        <v>2</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰潢汰無汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰潢汰無汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="2"/>
@@ -824,25 +856,26 @@
         </is>
       </c>
       <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>8</v>
+      </c>
+      <c r="F9" s="2">
         <v>2</v>
       </c>
-      <c r="D9" s="2">
-        <v>2</v>
-      </c>
-      <c r="E9" s="2">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -859,28 +892,34 @@
         </is>
       </c>
       <c r="C10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢太</t>
+          <t xml:space="preserve">湳|㳞|㳞</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢太</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
+          <t xml:space="preserve">湳
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어기야</t>
+        </is>
+      </c>
       <c r="J10" s="4"/>
       <c r="K10" s="2"/>
     </row>
@@ -894,28 +933,33 @@
         </is>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2">
         <v>3</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢太汰無汰</t>
+          <t xml:space="preserve">㳞|–㳞</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢太汰無汰</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
+          <t xml:space="preserve">㳞
+–㳞</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디야</t>
+        </is>
+      </c>
       <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
@@ -929,25 +973,25 @@
         </is>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無無無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無無無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -964,25 +1008,25 @@
         </is>
       </c>
       <c r="C13" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△無無無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△無無無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="2"/>
@@ -999,25 +1043,25 @@
         </is>
       </c>
       <c r="C14" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F14" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="2"/>
@@ -1034,25 +1078,25 @@
         </is>
       </c>
       <c r="C15" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I15" s="2"/>
@@ -1069,25 +1113,25 @@
         </is>
       </c>
       <c r="C16" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I16" s="2"/>
@@ -1104,25 +1148,27 @@
         </is>
       </c>
       <c r="C17" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F17" s="2">
         <v>4</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢|㳞|潢</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢
+㳞
+潢</t>
         </is>
       </c>
       <c r="I17" s="2"/>
@@ -1139,10 +1185,10 @@
         </is>
       </c>
       <c r="C18" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -1152,15 +1198,20 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰|–潢</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
+          <t xml:space="preserve">汰
+–潢</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에헤</t>
+        </is>
+      </c>
       <c r="J18" s="4"/>
       <c r="K18" s="2"/>
     </row>
@@ -1174,25 +1225,25 @@
         </is>
       </c>
       <c r="C19" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2">
+        <v>6</v>
+      </c>
+      <c r="F19" s="2">
         <v>2</v>
       </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="I19" s="2"/>
@@ -1209,28 +1260,33 @@
         </is>
       </c>
       <c r="C20" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢|–汰</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I20" s="2"/>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에헤</t>
+        </is>
+      </c>
       <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
@@ -1244,29 +1300,39 @@
         </is>
       </c>
       <c r="C21" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F21" s="2">
         <v>2</v>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="4"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|汰|–</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+汰
+–</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에에</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無·汰 겹쳐 씀</t>
+        </is>
+      </c>
       <c r="K21" s="2"/>
     </row>
     <row r="22">
@@ -1279,29 +1345,38 @@
         </is>
       </c>
       <c r="C22" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" s="2">
         <v>3</v>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="4"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|–汰</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에헤</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰 오른쪽 세로 물결선</t>
+        </is>
+      </c>
       <c r="K22" s="2"/>
     </row>
     <row r="23">
@@ -1314,29 +1389,39 @@
         </is>
       </c>
       <c r="C23" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F23" s="2">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|汰|–</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+汰
+–</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에어</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無·汰 겹쳐 씀</t>
+        </is>
+      </c>
       <c r="K23" s="2"/>
     </row>
     <row r="24">
@@ -1349,28 +1434,33 @@
         </is>
       </c>
       <c r="C24" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">潢|–汰</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I24" s="2"/>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
       <c r="J24" s="4"/>
       <c r="K24" s="2"/>
     </row>
@@ -1384,29 +1474,35 @@
         </is>
       </c>
       <c r="C25" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F25" s="2">
-        <v>2</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I25" s="2"/>
-      <c r="J25" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|汰|·</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+汰
+·</t>
+        </is>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아래 작은 점</t>
+        </is>
+      </c>
       <c r="K25" s="2"/>
     </row>
     <row r="26">
@@ -1419,29 +1515,35 @@
         </is>
       </c>
       <c r="C26" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F26" s="2">
-        <v>2</v>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南|仲</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가운데 古 모양→南 흘림으로 봄. 가사 칸엔 ㄹ/ㅣ 모양 표시만</t>
+        </is>
+      </c>
       <c r="K26" s="2"/>
     </row>
     <row r="27">
@@ -1454,25 +1556,25 @@
         </is>
       </c>
       <c r="C27" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F27" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢太</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢太</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I27" s="2"/>
@@ -1489,25 +1591,25 @@
         </is>
       </c>
       <c r="C28" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I28" s="2"/>
@@ -1524,25 +1626,25 @@
         </is>
       </c>
       <c r="C29" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D29" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E29" s="2">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I29" s="2"/>
@@ -1559,25 +1661,25 @@
         </is>
       </c>
       <c r="C30" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D30" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I30" s="2"/>
@@ -1594,25 +1696,25 @@
         </is>
       </c>
       <c r="C31" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -1629,25 +1731,25 @@
         </is>
       </c>
       <c r="C32" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D32" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰無汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰無汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I32" s="2"/>
@@ -1664,33 +1766,3887 @@
         </is>
       </c>
       <c r="C33" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D33" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E33" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F33" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="4"/>
       <c r="K33" s="2"/>
     </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C34" s="2">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2">
+        <v>3</v>
+      </c>
+      <c r="E34" s="2">
+        <v>5</v>
+      </c>
+      <c r="F34" s="2">
+        <v>2</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J34" s="4"/>
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>1</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C35" s="2">
+        <v>3</v>
+      </c>
+      <c r="D35" s="2">
+        <v>3</v>
+      </c>
+      <c r="E35" s="2">
+        <v>6</v>
+      </c>
+      <c r="F35" s="2">
+        <v>2</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古 모양→南 흘림으로 봄</t>
+        </is>
+      </c>
+      <c r="K35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>1</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C36" s="2">
+        <v>3</v>
+      </c>
+      <c r="D36" s="2">
+        <v>3</v>
+      </c>
+      <c r="E36" s="2">
+        <v>7</v>
+      </c>
+      <c r="F36" s="2">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J36" s="4"/>
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>1</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C37" s="2">
+        <v>3</v>
+      </c>
+      <c r="D37" s="2">
+        <v>3</v>
+      </c>
+      <c r="E37" s="2">
+        <v>8</v>
+      </c>
+      <c r="F37" s="2">
+        <v>2</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J37" s="4"/>
+      <c r="K37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>1</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C38" s="2">
+        <v>3</v>
+      </c>
+      <c r="D38" s="2">
+        <v>3</v>
+      </c>
+      <c r="E38" s="2">
+        <v>9</v>
+      </c>
+      <c r="F38" s="2">
+        <v>3</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰|–㳞</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–㳞</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J38" s="4"/>
+      <c r="K38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>1</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C39" s="2">
+        <v>3</v>
+      </c>
+      <c r="D39" s="2">
+        <v>3</v>
+      </c>
+      <c r="E39" s="2">
+        <v>10</v>
+      </c>
+      <c r="F39" s="2">
+        <v>3</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|㳞|潢</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㳞
+潢</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J39" s="4"/>
+      <c r="K39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>1</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C40" s="2">
+        <v>3</v>
+      </c>
+      <c r="D40" s="2">
+        <v>3</v>
+      </c>
+      <c r="E40" s="2">
+        <v>11</v>
+      </c>
+      <c r="F40" s="2">
+        <v>3</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰|潢|汰</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢
+汰</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J40" s="4"/>
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>1</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C41" s="2">
+        <v>3</v>
+      </c>
+      <c r="D41" s="2">
+        <v>3</v>
+      </c>
+      <c r="E41" s="2">
+        <v>12</v>
+      </c>
+      <c r="F41" s="2">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南|仲</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南 古 모양. 이 칸 아래 경계 굵게 덧그음</t>
+        </is>
+      </c>
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>1</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C42" s="2">
+        <v>3</v>
+      </c>
+      <c r="D42" s="2">
+        <v>3</v>
+      </c>
+      <c r="E42" s="2">
+        <v>13</v>
+      </c>
+      <c r="F42" s="2">
+        <v>4</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–無</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에야</t>
+        </is>
+      </c>
+      <c r="J42" s="4"/>
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>1</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C43" s="2">
+        <v>3</v>
+      </c>
+      <c r="D43" s="2">
+        <v>3</v>
+      </c>
+      <c r="E43" s="2">
+        <v>14</v>
+      </c>
+      <c r="F43" s="2">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–無</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어야</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 끝 글자 야/아?</t>
+        </is>
+      </c>
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>1</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C44" s="2">
+        <v>3</v>
+      </c>
+      <c r="D44" s="2">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2">
+        <v>15</v>
+      </c>
+      <c r="F44" s="2">
+        <v>4</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>1</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C45" s="2">
+        <v>3</v>
+      </c>
+      <c r="D45" s="2">
+        <v>3</v>
+      </c>
+      <c r="E45" s="2">
+        <v>16</v>
+      </c>
+      <c r="F45" s="2">
+        <v>4</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I45" s="2"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>1</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C46" s="2">
+        <v>4</v>
+      </c>
+      <c r="D46" s="2">
+        <v>4</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰|–潢</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–潢</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달은</t>
+        </is>
+      </c>
+      <c r="J46" s="4"/>
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>1</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C47" s="2">
+        <v>4</v>
+      </c>
+      <c r="D47" s="2">
+        <v>4</v>
+      </c>
+      <c r="E47" s="2">
+        <v>2</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|–潢</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–潢</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밝고</t>
+        </is>
+      </c>
+      <c r="J47" s="4"/>
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>1</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C48" s="2">
+        <v>4</v>
+      </c>
+      <c r="D48" s="2">
+        <v>4</v>
+      </c>
+      <c r="E48" s="2">
+        <v>3</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I48" s="2"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>1</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C49" s="2">
+        <v>4</v>
+      </c>
+      <c r="D49" s="2">
+        <v>4</v>
+      </c>
+      <c r="E49" s="2">
+        <v>4</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I49" s="3"/>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△ 덧그어 흐림</t>
+        </is>
+      </c>
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>1</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C50" s="2">
+        <v>4</v>
+      </c>
+      <c r="D50" s="2">
+        <v>4</v>
+      </c>
+      <c r="E50" s="2">
+        <v>5</v>
+      </c>
+      <c r="F50" s="2">
+        <v>2</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I50" s="2"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>1</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C51" s="2">
+        <v>4</v>
+      </c>
+      <c r="D51" s="2">
+        <v>4</v>
+      </c>
+      <c r="E51" s="2">
+        <v>6</v>
+      </c>
+      <c r="F51" s="2">
+        <v>2</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I51" s="2"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>1</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C52" s="2">
+        <v>4</v>
+      </c>
+      <c r="D52" s="2">
+        <v>4</v>
+      </c>
+      <c r="E52" s="2">
+        <v>7</v>
+      </c>
+      <c r="F52" s="2">
+        <v>2</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|–汰</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오오</t>
+        </is>
+      </c>
+      <c r="J52" s="4"/>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>1</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C53" s="2">
+        <v>4</v>
+      </c>
+      <c r="D53" s="2">
+        <v>4</v>
+      </c>
+      <c r="E53" s="2">
+        <v>8</v>
+      </c>
+      <c r="F53" s="2">
+        <v>2</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–汰</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–汰</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오오</t>
+        </is>
+      </c>
+      <c r="J53" s="4"/>
+      <c r="K53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>1</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C54" s="2">
+        <v>4</v>
+      </c>
+      <c r="D54" s="2">
+        <v>4</v>
+      </c>
+      <c r="E54" s="2">
+        <v>9</v>
+      </c>
+      <c r="F54" s="2">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|–汰</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">명랑</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 랑/강?</t>
+        </is>
+      </c>
+      <c r="K54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>1</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C55" s="2">
+        <v>4</v>
+      </c>
+      <c r="D55" s="2">
+        <v>4</v>
+      </c>
+      <c r="E55" s="2">
+        <v>10</v>
+      </c>
+      <c r="F55" s="2">
+        <v>3</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–無</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한데</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 한/천?</t>
+        </is>
+      </c>
+      <c r="K55" s="2"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>1</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C56" s="2">
+        <v>4</v>
+      </c>
+      <c r="D56" s="2">
+        <v>4</v>
+      </c>
+      <c r="E56" s="2">
+        <v>11</v>
+      </c>
+      <c r="F56" s="2">
+        <v>3</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I56" s="2"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>1</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C57" s="2">
+        <v>4</v>
+      </c>
+      <c r="D57" s="2">
+        <v>4</v>
+      </c>
+      <c r="E57" s="2">
+        <v>12</v>
+      </c>
+      <c r="F57" s="2">
+        <v>3</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I57" s="2"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>1</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C58" s="2">
+        <v>4</v>
+      </c>
+      <c r="D58" s="2">
+        <v>4</v>
+      </c>
+      <c r="E58" s="2">
+        <v>13</v>
+      </c>
+      <c r="F58" s="2">
+        <v>4</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|–潢</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–潢</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고향</t>
+        </is>
+      </c>
+      <c r="J58" s="4"/>
+      <c r="K58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>1</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C59" s="2">
+        <v>4</v>
+      </c>
+      <c r="D59" s="2">
+        <v>4</v>
+      </c>
+      <c r="E59" s="2">
+        <v>14</v>
+      </c>
+      <c r="F59" s="2">
+        <v>4</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|–㳞</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–㳞</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생각</t>
+        </is>
+      </c>
+      <c r="J59" s="4"/>
+      <c r="K59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>1</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C60" s="2">
+        <v>4</v>
+      </c>
+      <c r="D60" s="2">
+        <v>4</v>
+      </c>
+      <c r="E60" s="2">
+        <v>15</v>
+      </c>
+      <c r="F60" s="2">
+        <v>4</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I60" s="2"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>1</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C61" s="2">
+        <v>4</v>
+      </c>
+      <c r="D61" s="2">
+        <v>4</v>
+      </c>
+      <c r="E61" s="2">
+        <v>16</v>
+      </c>
+      <c r="F61" s="2">
+        <v>4</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I61" s="2"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <v>1</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C62" s="2">
+        <v>5</v>
+      </c>
+      <c r="D62" s="2">
+        <v>5</v>
+      </c>
+      <c r="E62" s="2">
+        <v>1</v>
+      </c>
+      <c r="F62" s="2">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I62" s="2"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <v>1</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C63" s="2">
+        <v>5</v>
+      </c>
+      <c r="D63" s="2">
+        <v>5</v>
+      </c>
+      <c r="E63" s="2">
+        <v>2</v>
+      </c>
+      <c r="F63" s="2">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I63" s="2"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <v>1</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C64" s="2">
+        <v>5</v>
+      </c>
+      <c r="D64" s="2">
+        <v>5</v>
+      </c>
+      <c r="E64" s="2">
+        <v>3</v>
+      </c>
+      <c r="F64" s="2">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|–潢</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–潢</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아아</t>
+        </is>
+      </c>
+      <c r="J64" s="4"/>
+      <c r="K64" s="2"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>1</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C65" s="2">
+        <v>5</v>
+      </c>
+      <c r="D65" s="2">
+        <v>5</v>
+      </c>
+      <c r="E65" s="2">
+        <v>4</v>
+      </c>
+      <c r="F65" s="2">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰|–潢</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–潢</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아아</t>
+        </is>
+      </c>
+      <c r="J65" s="4"/>
+      <c r="K65" s="2"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2">
+        <v>1</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C66" s="2">
+        <v>5</v>
+      </c>
+      <c r="D66" s="2">
+        <v>5</v>
+      </c>
+      <c r="E66" s="2">
+        <v>5</v>
+      </c>
+      <c r="F66" s="2">
+        <v>2</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|–汰</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">절로</t>
+        </is>
+      </c>
+      <c r="J66" s="4"/>
+      <c r="K66" s="2"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2">
+        <v>1</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C67" s="2">
+        <v>5</v>
+      </c>
+      <c r="D67" s="2">
+        <v>5</v>
+      </c>
+      <c r="E67" s="2">
+        <v>6</v>
+      </c>
+      <c r="F67" s="2">
+        <v>2</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–無</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">난다</t>
+        </is>
+      </c>
+      <c r="J67" s="4"/>
+      <c r="K67" s="2"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2">
+        <v>1</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C68" s="2">
+        <v>5</v>
+      </c>
+      <c r="D68" s="2">
+        <v>5</v>
+      </c>
+      <c r="E68" s="2">
+        <v>7</v>
+      </c>
+      <c r="F68" s="2">
+        <v>2</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I68" s="2"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="2"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2">
+        <v>1</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C69" s="2">
+        <v>5</v>
+      </c>
+      <c r="D69" s="2">
+        <v>5</v>
+      </c>
+      <c r="E69" s="2">
+        <v>8</v>
+      </c>
+      <c r="F69" s="2">
+        <v>2</v>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I69" s="2"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="2"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2">
+        <v>1</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C70" s="2">
+        <v>5</v>
+      </c>
+      <c r="D70" s="2">
+        <v>5</v>
+      </c>
+      <c r="E70" s="2">
+        <v>9</v>
+      </c>
+      <c r="F70" s="2">
+        <v>3</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|汰|汰</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+汰
+汰</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어기야</t>
+        </is>
+      </c>
+      <c r="J70" s="4"/>
+      <c r="K70" s="2"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2">
+        <v>1</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C71" s="2">
+        <v>5</v>
+      </c>
+      <c r="D71" s="2">
+        <v>5</v>
+      </c>
+      <c r="E71" s="2">
+        <v>10</v>
+      </c>
+      <c r="F71" s="2">
+        <v>3</v>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–無</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디야</t>
+        </is>
+      </c>
+      <c r="J71" s="4"/>
+      <c r="K71" s="2"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2">
+        <v>1</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C72" s="2">
+        <v>5</v>
+      </c>
+      <c r="D72" s="2">
+        <v>5</v>
+      </c>
+      <c r="E72" s="2">
+        <v>12</v>
+      </c>
+      <c r="F72" s="2">
+        <v>3</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I72" s="2"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="2"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2">
+        <v>1</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C73" s="2">
+        <v>5</v>
+      </c>
+      <c r="D73" s="2">
+        <v>5</v>
+      </c>
+      <c r="E73" s="2">
+        <v>13</v>
+      </c>
+      <c r="F73" s="2">
+        <v>4</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳|㳞|㳞</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어기야</t>
+        </is>
+      </c>
+      <c r="J73" s="4"/>
+      <c r="K73" s="2"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2">
+        <v>1</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C74" s="2">
+        <v>5</v>
+      </c>
+      <c r="D74" s="2">
+        <v>5</v>
+      </c>
+      <c r="E74" s="2">
+        <v>14</v>
+      </c>
+      <c r="F74" s="2">
+        <v>4</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|–㳞</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–㳞</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디야</t>
+        </is>
+      </c>
+      <c r="J74" s="4"/>
+      <c r="K74" s="2"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2">
+        <v>1</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C75" s="2">
+        <v>5</v>
+      </c>
+      <c r="D75" s="2">
+        <v>5</v>
+      </c>
+      <c r="E75" s="2">
+        <v>15</v>
+      </c>
+      <c r="F75" s="2">
+        <v>4</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I75" s="2"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="2"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2">
+        <v>1</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C76" s="2">
+        <v>5</v>
+      </c>
+      <c r="D76" s="2">
+        <v>5</v>
+      </c>
+      <c r="E76" s="2">
+        <v>16</v>
+      </c>
+      <c r="F76" s="2">
+        <v>4</v>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I76" s="2"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="2"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2">
+        <v>1</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C77" s="2">
+        <v>6</v>
+      </c>
+      <c r="D77" s="2">
+        <v>6</v>
+      </c>
+      <c r="E77" s="2">
+        <v>1</v>
+      </c>
+      <c r="F77" s="2">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I77" s="2"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="2"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2">
+        <v>1</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C78" s="2">
+        <v>6</v>
+      </c>
+      <c r="D78" s="2">
+        <v>6</v>
+      </c>
+      <c r="E78" s="2">
+        <v>2</v>
+      </c>
+      <c r="F78" s="2">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I78" s="2"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="2"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2">
+        <v>1</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C79" s="2">
+        <v>6</v>
+      </c>
+      <c r="D79" s="2">
+        <v>6</v>
+      </c>
+      <c r="E79" s="2">
+        <v>3</v>
+      </c>
+      <c r="F79" s="2">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I79" s="2"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="2"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2">
+        <v>1</v>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C80" s="2">
+        <v>6</v>
+      </c>
+      <c r="D80" s="2">
+        <v>6</v>
+      </c>
+      <c r="E80" s="2">
+        <v>4</v>
+      </c>
+      <c r="F80" s="2">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|㳞|潢</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㳞
+潢</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J80" s="4"/>
+      <c r="K80" s="2"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2">
+        <v>1</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C81" s="2">
+        <v>6</v>
+      </c>
+      <c r="D81" s="2">
+        <v>6</v>
+      </c>
+      <c r="E81" s="2">
+        <v>5</v>
+      </c>
+      <c r="F81" s="2">
+        <v>2</v>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰|–潢</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–潢</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에헤</t>
+        </is>
+      </c>
+      <c r="J81" s="4"/>
+      <c r="K81" s="2"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2">
+        <v>1</v>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C82" s="2">
+        <v>6</v>
+      </c>
+      <c r="D82" s="2">
+        <v>6</v>
+      </c>
+      <c r="E82" s="2">
+        <v>6</v>
+      </c>
+      <c r="F82" s="2">
+        <v>2</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I82" s="2"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="2"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2">
+        <v>1</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C83" s="2">
+        <v>6</v>
+      </c>
+      <c r="D83" s="2">
+        <v>6</v>
+      </c>
+      <c r="E83" s="2">
+        <v>7</v>
+      </c>
+      <c r="F83" s="2">
+        <v>2</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I83" s="2"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="2"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2">
+        <v>1</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C84" s="2">
+        <v>6</v>
+      </c>
+      <c r="D84" s="2">
+        <v>6</v>
+      </c>
+      <c r="E84" s="2">
+        <v>8</v>
+      </c>
+      <c r="F84" s="2">
+        <v>2</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I84" s="2"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="2"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2">
+        <v>1</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C85" s="2">
+        <v>6</v>
+      </c>
+      <c r="D85" s="2">
+        <v>6</v>
+      </c>
+      <c r="E85" s="2">
+        <v>9</v>
+      </c>
+      <c r="F85" s="2">
+        <v>3</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I85" s="2"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="2"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2">
+        <v>1</v>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C86" s="2">
+        <v>6</v>
+      </c>
+      <c r="D86" s="2">
+        <v>6</v>
+      </c>
+      <c r="E86" s="2">
+        <v>10</v>
+      </c>
+      <c r="F86" s="2">
+        <v>3</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I86" s="2"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="2"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2">
+        <v>1</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C87" s="2">
+        <v>6</v>
+      </c>
+      <c r="D87" s="2">
+        <v>6</v>
+      </c>
+      <c r="E87" s="2">
+        <v>11</v>
+      </c>
+      <c r="F87" s="2">
+        <v>3</v>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|–汰</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에헤</t>
+        </is>
+      </c>
+      <c r="J87" s="4"/>
+      <c r="K87" s="2"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2">
+        <v>1</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C88" s="2">
+        <v>6</v>
+      </c>
+      <c r="D88" s="2">
+        <v>6</v>
+      </c>
+      <c r="E88" s="2">
+        <v>12</v>
+      </c>
+      <c r="F88" s="2">
+        <v>3</v>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–汰</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–汰</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에에</t>
+        </is>
+      </c>
+      <c r="J88" s="4"/>
+      <c r="K88" s="2"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2">
+        <v>1</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C89" s="2">
+        <v>6</v>
+      </c>
+      <c r="D89" s="2">
+        <v>6</v>
+      </c>
+      <c r="E89" s="2">
+        <v>13</v>
+      </c>
+      <c r="F89" s="2">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|–汰</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에헤</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">– 잘 안 보임</t>
+        </is>
+      </c>
+      <c r="K89" s="2"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2">
+        <v>1</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C90" s="2">
+        <v>6</v>
+      </c>
+      <c r="D90" s="2">
+        <v>6</v>
+      </c>
+      <c r="E90" s="2">
+        <v>14</v>
+      </c>
+      <c r="F90" s="2">
+        <v>4</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–汰</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–汰</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에헤</t>
+        </is>
+      </c>
+      <c r="J90" s="4"/>
+      <c r="K90" s="2"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2">
+        <v>1</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C91" s="2">
+        <v>6</v>
+      </c>
+      <c r="D91" s="2">
+        <v>6</v>
+      </c>
+      <c r="E91" s="2">
+        <v>15</v>
+      </c>
+      <c r="F91" s="2">
+        <v>4</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|–汰</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에헤</t>
+        </is>
+      </c>
+      <c r="J91" s="4"/>
+      <c r="K91" s="2"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2">
+        <v>1</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C92" s="2">
+        <v>6</v>
+      </c>
+      <c r="D92" s="2">
+        <v>6</v>
+      </c>
+      <c r="E92" s="2">
+        <v>16</v>
+      </c>
+      <c r="F92" s="2">
+        <v>4</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–汰</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–汰</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에헤</t>
+        </is>
+      </c>
+      <c r="J92" s="4"/>
+      <c r="K92" s="2"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2">
+        <v>1</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C93" s="2">
+        <v>7</v>
+      </c>
+      <c r="D93" s="2">
+        <v>7</v>
+      </c>
+      <c r="E93" s="2">
+        <v>1</v>
+      </c>
+      <c r="F93" s="2">
+        <v>1</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^|南|仲</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^
+南
+仲</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無 오른쪽 작은 꺾쇠, 南 古 모양</t>
+        </is>
+      </c>
+      <c r="K93" s="2"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2">
+        <v>1</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C94" s="2">
+        <v>7</v>
+      </c>
+      <c r="D94" s="2">
+        <v>7</v>
+      </c>
+      <c r="E94" s="2">
+        <v>2</v>
+      </c>
+      <c r="F94" s="2">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I94" s="2"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="2"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2">
+        <v>1</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C95" s="2">
+        <v>7</v>
+      </c>
+      <c r="D95" s="2">
+        <v>7</v>
+      </c>
+      <c r="E95" s="2">
+        <v>3</v>
+      </c>
+      <c r="F95" s="2">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I95" s="2"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="2"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2">
+        <v>1</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C96" s="2">
+        <v>7</v>
+      </c>
+      <c r="D96" s="2">
+        <v>7</v>
+      </c>
+      <c r="E96" s="2">
+        <v>4</v>
+      </c>
+      <c r="F96" s="2">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I96" s="2"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="2"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2">
+        <v>1</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C97" s="2">
+        <v>7</v>
+      </c>
+      <c r="D97" s="2">
+        <v>7</v>
+      </c>
+      <c r="E97" s="2">
+        <v>5</v>
+      </c>
+      <c r="F97" s="2">
+        <v>2</v>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I97" s="2"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="2"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2">
+        <v>1</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C98" s="2">
+        <v>7</v>
+      </c>
+      <c r="D98" s="2">
+        <v>7</v>
+      </c>
+      <c r="E98" s="2">
+        <v>6</v>
+      </c>
+      <c r="F98" s="2">
+        <v>2</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I98" s="2"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="2"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2">
+        <v>1</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C99" s="2">
+        <v>7</v>
+      </c>
+      <c r="D99" s="2">
+        <v>7</v>
+      </c>
+      <c r="E99" s="2">
+        <v>7</v>
+      </c>
+      <c r="F99" s="2">
+        <v>2</v>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I99" s="2"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="2"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2">
+        <v>1</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C100" s="2">
+        <v>7</v>
+      </c>
+      <c r="D100" s="2">
+        <v>7</v>
+      </c>
+      <c r="E100" s="2">
+        <v>8</v>
+      </c>
+      <c r="F100" s="2">
+        <v>2</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I100" s="2"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="2"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2">
+        <v>1</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C101" s="2">
+        <v>7</v>
+      </c>
+      <c r="D101" s="2">
+        <v>7</v>
+      </c>
+      <c r="E101" s="2">
+        <v>9</v>
+      </c>
+      <c r="F101" s="2">
+        <v>3</v>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J101" s="4"/>
+      <c r="K101" s="2"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2">
+        <v>1</v>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C102" s="2">
+        <v>7</v>
+      </c>
+      <c r="D102" s="2">
+        <v>7</v>
+      </c>
+      <c r="E102" s="2">
+        <v>10</v>
+      </c>
+      <c r="F102" s="2">
+        <v>3</v>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古 모양→南 흘림으로 봄</t>
+        </is>
+      </c>
+      <c r="K102" s="2"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2">
+        <v>1</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C103" s="2">
+        <v>7</v>
+      </c>
+      <c r="D103" s="2">
+        <v>7</v>
+      </c>
+      <c r="E103" s="2">
+        <v>11</v>
+      </c>
+      <c r="F103" s="2">
+        <v>3</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J103" s="4"/>
+      <c r="K103" s="2"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2">
+        <v>1</v>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C104" s="2">
+        <v>7</v>
+      </c>
+      <c r="D104" s="2">
+        <v>7</v>
+      </c>
+      <c r="E104" s="2">
+        <v>12</v>
+      </c>
+      <c r="F104" s="2">
+        <v>3</v>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="J104" s="4"/>
+      <c r="K104" s="2"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2">
+        <v>1</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C105" s="2">
+        <v>7</v>
+      </c>
+      <c r="D105" s="2">
+        <v>7</v>
+      </c>
+      <c r="E105" s="2">
+        <v>13</v>
+      </c>
+      <c r="F105" s="2">
+        <v>4</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰|–㳞</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–㳞</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에헤</t>
+        </is>
+      </c>
+      <c r="J105" s="4"/>
+      <c r="K105" s="2"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2">
+        <v>1</v>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C106" s="2">
+        <v>7</v>
+      </c>
+      <c r="D106" s="2">
+        <v>7</v>
+      </c>
+      <c r="E106" s="2">
+        <v>14</v>
+      </c>
+      <c r="F106" s="2">
+        <v>4</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|㳞|潢</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㳞
+潢</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+      <c r="J106" s="4"/>
+      <c r="K106" s="2"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2">
+        <v>1</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C107" s="2">
+        <v>7</v>
+      </c>
+      <c r="D107" s="2">
+        <v>7</v>
+      </c>
+      <c r="E107" s="2">
+        <v>15</v>
+      </c>
+      <c r="F107" s="2">
+        <v>4</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰|潢|汰</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢
+汰</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J107" s="4"/>
+      <c r="K107" s="2"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2">
+        <v>1</v>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C108" s="2">
+        <v>7</v>
+      </c>
+      <c r="D108" s="2">
+        <v>7</v>
+      </c>
+      <c r="E108" s="2">
+        <v>16</v>
+      </c>
+      <c r="F108" s="2">
+        <v>4</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南|仲</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J108" s="4"/>
+      <c r="K108" s="2"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2">
+        <v>1</v>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C109" s="2">
+        <v>8</v>
+      </c>
+      <c r="D109" s="2">
+        <v>8</v>
+      </c>
+      <c r="E109" s="2">
+        <v>1</v>
+      </c>
+      <c r="F109" s="2">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–無</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어야</t>
+        </is>
+      </c>
+      <c r="J109" s="4"/>
+      <c r="K109" s="2"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2">
+        <v>1</v>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C110" s="2">
+        <v>8</v>
+      </c>
+      <c r="D110" s="2">
+        <v>8</v>
+      </c>
+      <c r="E110" s="2">
+        <v>2</v>
+      </c>
+      <c r="F110" s="2">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–無</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디야</t>
+        </is>
+      </c>
+      <c r="J110" s="4"/>
+      <c r="K110" s="2"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2">
+        <v>1</v>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C111" s="2">
+        <v>8</v>
+      </c>
+      <c r="D111" s="2">
+        <v>8</v>
+      </c>
+      <c r="E111" s="2">
+        <v>3</v>
+      </c>
+      <c r="F111" s="2">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I111" s="2"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="2"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2">
+        <v>1</v>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C112" s="2">
+        <v>8</v>
+      </c>
+      <c r="D112" s="2">
+        <v>8</v>
+      </c>
+      <c r="E112" s="2">
+        <v>4</v>
+      </c>
+      <c r="F112" s="2">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I112" s="2"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="2"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2">
+        <v>1</v>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C113" s="2">
+        <v>8</v>
+      </c>
+      <c r="D113" s="2">
+        <v>8</v>
+      </c>
+      <c r="E113" s="2">
+        <v>5</v>
+      </c>
+      <c r="F113" s="2">
+        <v>2</v>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰|無|無</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+無
+無</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어기야</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가운데 글자 無 윗부분만 보임</t>
+        </is>
+      </c>
+      <c r="K113" s="2"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2">
+        <v>1</v>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C114" s="2">
+        <v>8</v>
+      </c>
+      <c r="D114" s="2">
+        <v>8</v>
+      </c>
+      <c r="E114" s="2">
+        <v>6</v>
+      </c>
+      <c r="F114" s="2">
+        <v>2</v>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|無|無</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+無
+無</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어기야</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가운데 글자 太처럼도 보임</t>
+        </is>
+      </c>
+      <c r="K114" s="2"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2">
+        <v>1</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C115" s="2">
+        <v>8</v>
+      </c>
+      <c r="D115" s="2">
+        <v>8</v>
+      </c>
+      <c r="E115" s="2">
+        <v>7</v>
+      </c>
+      <c r="F115" s="2">
+        <v>2</v>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I115" s="2"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="2"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2">
+        <v>1</v>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C116" s="2">
+        <v>8</v>
+      </c>
+      <c r="D116" s="2">
+        <v>8</v>
+      </c>
+      <c r="E116" s="2">
+        <v>8</v>
+      </c>
+      <c r="F116" s="2">
+        <v>2</v>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I116" s="3"/>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작은 동그라미. 가사 칸에 日 모양(ㅂ?)</t>
+        </is>
+      </c>
+      <c r="K116" s="2"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2">
+        <v>1</v>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C117" s="2">
+        <v>8</v>
+      </c>
+      <c r="D117" s="2">
+        <v>8</v>
+      </c>
+      <c r="E117" s="2">
+        <v>9</v>
+      </c>
+      <c r="F117" s="2">
+        <v>3</v>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I117" s="2"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="2"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2">
+        <v>1</v>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C118" s="2">
+        <v>8</v>
+      </c>
+      <c r="D118" s="2">
+        <v>8</v>
+      </c>
+      <c r="E118" s="2">
+        <v>10</v>
+      </c>
+      <c r="F118" s="2">
+        <v>3</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I118" s="2"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="2"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2">
+        <v>1</v>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C119" s="2">
+        <v>9</v>
+      </c>
+      <c r="D119" s="2">
+        <v>9</v>
+      </c>
+      <c r="E119" s="2">
+        <v>1</v>
+      </c>
+      <c r="F119" s="2">
+        <v>1</v>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J119" s="4"/>
+      <c r="K119" s="2"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2">
+        <v>1</v>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C120" s="2">
+        <v>9</v>
+      </c>
+      <c r="D120" s="2">
+        <v>9</v>
+      </c>
+      <c r="E120" s="2">
+        <v>2</v>
+      </c>
+      <c r="F120" s="2">
+        <v>1</v>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기</t>
+        </is>
+      </c>
+      <c r="J120" s="4"/>
+      <c r="K120" s="2"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2">
+        <v>1</v>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C121" s="2">
+        <v>9</v>
+      </c>
+      <c r="D121" s="2">
+        <v>9</v>
+      </c>
+      <c r="E121" s="2">
+        <v>3</v>
+      </c>
+      <c r="F121" s="2">
+        <v>1</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|汰</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+汰</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="J121" s="4"/>
+      <c r="K121" s="2"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2">
+        <v>1</v>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C122" s="2">
+        <v>9</v>
+      </c>
+      <c r="D122" s="2">
+        <v>9</v>
+      </c>
+      <c r="E122" s="2">
+        <v>4</v>
+      </c>
+      <c r="F122" s="2">
+        <v>1</v>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="J122" s="4"/>
+      <c r="K122" s="2"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2">
+        <v>1</v>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C123" s="2">
+        <v>9</v>
+      </c>
+      <c r="D123" s="2">
+        <v>9</v>
+      </c>
+      <c r="E123" s="2">
+        <v>5</v>
+      </c>
+      <c r="F123" s="2">
+        <v>2</v>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">차</t>
+        </is>
+      </c>
+      <c r="J123" s="4"/>
+      <c r="K123" s="2"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2">
+        <v>1</v>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C124" s="2">
+        <v>9</v>
+      </c>
+      <c r="D124" s="2">
+        <v>9</v>
+      </c>
+      <c r="E124" s="2">
+        <v>6</v>
+      </c>
+      <c r="F124" s="2">
+        <v>2</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|潢</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="I124" s="2"/>
+      <c r="J124" s="4"/>
+      <c r="K124" s="2"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2">
+        <v>1</v>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C125" s="2">
+        <v>9</v>
+      </c>
+      <c r="D125" s="2">
+        <v>9</v>
+      </c>
+      <c r="E125" s="2">
+        <v>7</v>
+      </c>
+      <c r="F125" s="2">
+        <v>2</v>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">뱃</t>
+        </is>
+      </c>
+      <c r="J125" s="4"/>
+      <c r="K125" s="2"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2">
+        <v>1</v>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C126" s="2">
+        <v>9</v>
+      </c>
+      <c r="D126" s="2">
+        <v>9</v>
+      </c>
+      <c r="E126" s="2">
+        <v>8</v>
+      </c>
+      <c r="F126" s="2">
+        <v>2</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노</t>
+        </is>
+      </c>
+      <c r="J126" s="4"/>
+      <c r="K126" s="2"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2">
+        <v>1</v>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C127" s="2">
+        <v>9</v>
+      </c>
+      <c r="D127" s="2">
+        <v>9</v>
+      </c>
+      <c r="E127" s="2">
+        <v>9</v>
+      </c>
+      <c r="F127" s="2">
+        <v>3</v>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|汰</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+汰</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 래?</t>
+        </is>
+      </c>
+      <c r="K127" s="2"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2">
+        <v>1</v>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C128" s="2">
+        <v>9</v>
+      </c>
+      <c r="D128" s="2">
+        <v>9</v>
+      </c>
+      <c r="E128" s="2">
+        <v>10</v>
+      </c>
+      <c r="F128" s="2">
+        <v>3</v>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南 古 모양</t>
+        </is>
+      </c>
+      <c r="K128" s="2"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2">
+        <v>1</v>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C129" s="2">
+        <v>9</v>
+      </c>
+      <c r="D129" s="2">
+        <v>9</v>
+      </c>
+      <c r="E129" s="2">
+        <v>11</v>
+      </c>
+      <c r="F129" s="2">
+        <v>3</v>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I129" s="2"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="2"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2">
+        <v>1</v>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C130" s="2">
+        <v>9</v>
+      </c>
+      <c r="D130" s="2">
+        <v>9</v>
+      </c>
+      <c r="E130" s="2">
+        <v>12</v>
+      </c>
+      <c r="F130" s="2">
+        <v>3</v>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잔</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古 모양→南 흘림으로 봄</t>
+        </is>
+      </c>
+      <c r="K130" s="2"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2">
+        <v>1</v>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C131" s="2">
+        <v>9</v>
+      </c>
+      <c r="D131" s="2">
+        <v>9</v>
+      </c>
+      <c r="E131" s="2">
+        <v>13</v>
+      </c>
+      <c r="F131" s="2">
+        <v>4</v>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="J131" s="4"/>
+      <c r="K131" s="2"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2">
+        <v>1</v>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C132" s="2">
+        <v>9</v>
+      </c>
+      <c r="D132" s="2">
+        <v>9</v>
+      </c>
+      <c r="E132" s="2">
+        <v>14</v>
+      </c>
+      <c r="F132" s="2">
+        <v>4</v>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I132" s="2"/>
+      <c r="J132" s="4"/>
+      <c r="K132" s="2"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2">
+        <v>1</v>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="C133" s="2">
+        <v>9</v>
+      </c>
+      <c r="D133" s="2">
+        <v>9</v>
+      </c>
+      <c r="E133" s="2">
+        <v>15</v>
+      </c>
+      <c r="F133" s="2">
+        <v>4</v>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·|△</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·
+△</t>
+        </is>
+      </c>
+      <c r="I133" s="2"/>
+      <c r="J133" s="4"/>
+      <c r="K133" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K33"/>
+  <autoFilter ref="A1:K133"/>
 </worksheet>
 </file>
 
@@ -1710,12 +5666,18 @@
     <col min="11" max="11" width="6" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="6" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="17" max="17" width="6" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
+    <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="81.3" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1733,321 +5695,1296 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
-    </row>
-    <row r="3" ht="55.19" customHeight="1">
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+    </row>
+    <row r="3" ht="81.3" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C3" s="25"/>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G3" s="25"/>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+야</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^
+南
+仲</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無無無</t>
-        </is>
-      </c>
-      <c r="I3" s="25"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無汰</t>
-        </is>
-      </c>
-      <c r="K3" s="25"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="M3" s="25"/>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
+          <t xml:space="preserve">汰
+–潢</t>
+        </is>
+      </c>
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달
+은</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O3" s="22"/>
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–潢</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+헤</t>
+        </is>
+      </c>
+      <c r="R3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^
+–無</t>
+        </is>
+      </c>
+      <c r="S3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="81.3" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C4" s="26"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기</t>
+        </is>
+      </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E4" s="26"/>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디
+야</t>
+        </is>
+      </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I4" s="25"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K4" s="25"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–潢</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밝
+고</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O4" s="25"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="S4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="81.3" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+汰</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E5" s="25"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G5" s="25"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I5" s="25"/>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–潢</t>
+        </is>
+      </c>
+      <c r="K5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+아</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M5" s="25"/>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O5" s="25"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S5" s="25"/>
+    </row>
+    <row r="6" ht="81.3" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="26"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞汰潢汰無汰</t>
-        </is>
-      </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞汰</t>
-        </is>
-      </c>
-      <c r="M4" s="26"/>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
-      <c r="A5" s="0"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△無無無</t>
-        </is>
-      </c>
-      <c r="I5" s="27"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K5" s="27"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M5" s="27"/>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="25"/>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="25"/>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="E6" s="26"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G6" s="26"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㳞
+潢</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–潢</t>
+        </is>
+      </c>
+      <c r="K6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+아</t>
+        </is>
+      </c>
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="M6" s="27"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="O6" s="26"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="S6" s="26"/>
+    </row>
+    <row r="7" ht="81.3" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="26"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">차</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+無
+無</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+기
+야</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">汰
+–潢</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+헤</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">절
+로</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I7" s="26"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="26"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
+      <c r="O7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+汰
+黃</t>
+        </is>
+      </c>
+      <c r="S7" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+기
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="81.3" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰無汰</t>
-        </is>
-      </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E8" s="27"/>
+          <t xml:space="preserve">㳞
+潢</t>
+        </is>
+      </c>
+      <c r="C8" s="25"/>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+無
+無</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+기
+야</t>
+        </is>
+      </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G8" s="27"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G8" s="25"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I8" s="27"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I8" s="25"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢太</t>
-        </is>
-      </c>
-      <c r="K8" s="27"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="27"/>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="K8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">난
+다</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M8" s="25"/>
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O8" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="S8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="81.3" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="25"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">뱃</t>
+        </is>
+      </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢太</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E9" s="25"/>
-      <c r="F9" s="21"/>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
       <c r="G9" s="25"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I9" s="25"/>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K9" s="25"/>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="M9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오
+오</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I9" s="25"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="25"/>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
+      <c r="O9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="Q9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+헤</t>
+        </is>
+      </c>
+      <c r="R9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S9" s="25"/>
+    </row>
+    <row r="10" ht="81.3" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="26"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E10" s="27"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="G10" s="26"/>
-      <c r="H10" s="21"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
       <c r="I10" s="26"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞潢太汰無汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="26"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="26"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–汰</t>
+        </is>
+      </c>
+      <c r="M10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오
+오</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="O10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="P10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+汰
+–</t>
+        </is>
+      </c>
+      <c r="Q10" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+에</t>
+        </is>
+      </c>
+      <c r="R10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="S10" s="26"/>
+    </row>
+    <row r="11" ht="81.3" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="27"/>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+汰</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E11" s="22"/>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="27"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I11" s="22"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+汰
+汰</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+기
+야</t>
+        </is>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="M11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">명
+랑</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–㳞</t>
+        </is>
+      </c>
+      <c r="O11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="P11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="Q11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+헤</t>
+        </is>
+      </c>
+      <c r="R11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="S11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+기
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="81.3" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="21"/>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
       <c r="E12" s="25"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="21"/>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
       <c r="I12" s="25"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰無汰</t>
-        </is>
-      </c>
-      <c r="M12" s="25"/>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="K12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디
+야</t>
+        </is>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="M12" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한
+데</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㳞
+潢</t>
+        </is>
+      </c>
+      <c r="O12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+汰
+–</t>
+        </is>
+      </c>
+      <c r="Q12" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+어</t>
+        </is>
+      </c>
+      <c r="R12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–㳞</t>
+        </is>
+      </c>
+      <c r="S12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="81.3" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="26"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C13" s="25"/>
       <c r="D13" s="21"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="26"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I13" s="26"/>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+헤</t>
+        </is>
+      </c>
       <c r="J13" s="21"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="26"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢
+汰</t>
+        </is>
+      </c>
+      <c r="O13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="Q13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="R13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S13" s="25"/>
+    </row>
+    <row r="14" ht="81.3" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="27"/>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잔</t>
+        </is>
+      </c>
       <c r="D14" s="21"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="27"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–汰</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+에</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K14" s="26"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M14" s="27"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="M14" s="26"/>
+      <c r="N14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="O14" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+汰
+–</t>
+        </is>
+      </c>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S14" s="26"/>
+    </row>
+    <row r="15" ht="81.3" customHeight="1">
+      <c r="A15" s="0"/>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–㳞</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+헤</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+헤</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+기
+야</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–潢</t>
+        </is>
+      </c>
+      <c r="M15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고
+향</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="O15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+야</t>
+        </is>
+      </c>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S15" s="22"/>
+    </row>
+    <row r="16" ht="81.3" customHeight="1">
+      <c r="A16" s="0"/>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㳞
+潢</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–汰</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+헤</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–㳞</t>
+        </is>
+      </c>
+      <c r="K16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디
+야</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–㳞</t>
+        </is>
+      </c>
+      <c r="M16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생
+각</t>
+        </is>
+      </c>
+      <c r="N16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="O16" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+야</t>
+        </is>
+      </c>
+      <c r="P16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S16" s="25"/>
+    </row>
+    <row r="17" ht="81.3" customHeight="1">
+      <c r="A17" s="0"/>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢
+汰</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–汰</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+헤</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K17" s="25"/>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M17" s="25"/>
+      <c r="N17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O17" s="25"/>
+      <c r="P17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S17" s="25"/>
+    </row>
+    <row r="18" ht="81.3" customHeight="1">
+      <c r="A18" s="0"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="G18" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–汰</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+헤</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K18" s="26"/>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M18" s="26"/>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O18" s="26"/>
+      <c r="P18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㳞
+潢</t>
+        </is>
+      </c>
+      <c r="S18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B2:S2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/잦은 뱃노리.xlsx
+++ b/sheets/민요/검수/잦은 뱃노리.xlsx
@@ -406,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 선 4칸마다) → 4/4·16. 오른쪽 끝 빈 줄 1개 제외하고 9줄. 머리 "잦은 뱃노래 &lt;자즌몰이&gt; 후렴", "3번". 古 모양 글자는 南 흘림으로 봄(仲·南·無 진행). 줄3 12정간 아래 굵은 덧줄, 줄2·6 일부 동그라미 묶음(생략). 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 선 4칸마다) → 4/4·16. 오른쪽 끝 빈 줄 1개 제외하고 9줄. 머리 "잦은 뱃노래 &lt;자즌몰이&gt; 후렴", "3번". 古 모양 글자는 南 흘림으로 봄(仲·南·無 진행). 줄3 12정간 아래 굵은 덧줄, 줄2·6 일부 동그라미 묶음(생략). 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|㳞|潢</t>
+          <t xml:space="preserve">㴌|㳞|㴌</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I17" s="2"/>
@@ -1198,13 +1198,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|–潢</t>
+          <t xml:space="preserve">汰|–㴌</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–汰</t>
+          <t xml:space="preserve">㴌|–汰</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–汰</t>
+          <t xml:space="preserve">㴌|–汰</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–汰</t>
+          <t xml:space="preserve">㴌|–汰</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -2015,14 +2015,14 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|㳞|潢</t>
+          <t xml:space="preserve">㴌|㳞|㴌</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2056,13 +2056,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|潢|汰</t>
+          <t xml:space="preserve">汰|㴌|汰</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢
+㴌
 汰</t>
         </is>
       </c>
@@ -2296,13 +2296,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|–潢</t>
+          <t xml:space="preserve">汰|–㴌</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2336,13 +2336,13 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|–潢</t>
+          <t xml:space="preserve">㳞|–㴌</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–汰</t>
+          <t xml:space="preserve">㴌|–汰</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–汰</t>
+          <t xml:space="preserve">㴌|–汰</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -2760,13 +2760,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|–潢</t>
+          <t xml:space="preserve">㳞|–㴌</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2980,13 +2980,13 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|–潢</t>
+          <t xml:space="preserve">㳞|–㴌</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3020,13 +3020,13 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|–潢</t>
+          <t xml:space="preserve">汰|–㴌</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–汰</t>
+          <t xml:space="preserve">㴌|–汰</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -3582,14 +3582,14 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|㳞|潢</t>
+          <t xml:space="preserve">㴌|㳞|㴌</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3623,13 +3623,13 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|–潢</t>
+          <t xml:space="preserve">汰|–㴌</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–汰</t>
+          <t xml:space="preserve">㴌|–汰</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–汰</t>
+          <t xml:space="preserve">㴌|–汰</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -4002,12 +4002,12 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–汰</t>
+          <t xml:space="preserve">㴌|–汰</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -4573,14 +4573,14 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|㳞|潢</t>
+          <t xml:space="preserve">㴌|㳞|㴌</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -4614,13 +4614,13 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|潢|汰</t>
+          <t xml:space="preserve">汰|㴌|汰</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢
+㴌
 汰</t>
         </is>
       </c>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -5278,13 +5278,13 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I124" s="2"/>
@@ -5353,12 +5353,12 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰</t>
+          <t xml:space="preserve">㴌|汰</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
@@ -5753,7 +5753,7 @@
       <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="M3" s="22" t="inlineStr">
@@ -5771,7 +5771,7 @@
       <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="Q3" s="22" t="inlineStr">
@@ -5797,7 +5797,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
@@ -5838,7 +5838,7 @@
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="M4" s="25" t="inlineStr">
@@ -5902,7 +5902,7 @@
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="K5" s="25" t="inlineStr">
@@ -5959,9 +5959,9 @@
       <c r="G6" s="26"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I6" s="26" t="inlineStr">
@@ -5972,7 +5972,7 @@
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="K6" s="26" t="inlineStr">
@@ -6040,7 +6040,7 @@
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -6099,7 +6099,7 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="C8" s="25"/>
@@ -6214,7 +6214,7 @@
       <c r="K9" s="25"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -6257,7 +6257,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C10" s="26" t="inlineStr">
@@ -6337,7 +6337,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="L11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="P11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -6494,9 +6494,9 @@
       </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="O12" s="25" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -6573,7 +6573,7 @@
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢
+㴌
 汰</t>
         </is>
       </c>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -6731,7 +6731,7 @@
       <c r="L15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="M15" s="22" t="inlineStr">
@@ -6779,9 +6779,9 @@
       <c r="E16" s="25"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
@@ -6864,7 +6864,7 @@
       <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢
+㴌
 汰</t>
         </is>
       </c>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
@@ -6972,9 +6972,9 @@
       <c r="Q18" s="26"/>
       <c r="R18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 㳞
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="S18" s="26"/>

--- a/sheets/민요/검수/잦은 뱃노리.xlsx
+++ b/sheets/민요/검수/잦은 뱃노리.xlsx
@@ -670,10 +670,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/잦은 뱃노리.xlsx
+++ b/sheets/민요/검수/잦은 뱃노리.xlsx
@@ -616,17 +616,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -743,7 +743,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -801,6 +801,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5277,778 +5321,778 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:S18"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="7" t="s">
+      <c r="H3" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="19"/>
+      <c r="J3" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="19"/>
+      <c r="L3" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="N3" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="O3" s="8"/>
-      <c r="P3" s="7" t="s">
+      <c r="N3" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="19"/>
+      <c r="P3" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="S3" s="21" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="7" t="s">
+      <c r="F4" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="22"/>
+      <c r="H4" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="22"/>
+      <c r="J4" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="22"/>
+      <c r="L4" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="N4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="O4" s="11"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="7" t="s">
+      <c r="N4" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" s="22"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="S4" s="11" t="s">
+      <c r="S4" s="22" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7" t="s">
+      <c r="D5" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="22"/>
+      <c r="F5" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="22"/>
+      <c r="H5" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="22"/>
+      <c r="J5" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="L5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="11"/>
-      <c r="N5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="S5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="L5" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="O5" s="22"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="S5" s="22"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B6" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="7" t="s">
+      <c r="E6" s="23"/>
+      <c r="F6" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="23"/>
+      <c r="H6" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="7" t="s">
+      <c r="M6" s="24"/>
+      <c r="N6" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="12"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="7" t="s">
+      <c r="O6" s="23"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="S6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="S6" s="23"/>
+    </row>
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7" t="s">
+      <c r="F7" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="7" t="s">
+      <c r="L7" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="19"/>
+      <c r="N7" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="9" t="s">
+      <c r="P7" s="18"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="S7" s="10" t="s">
+      <c r="S7" s="21" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="9" t="s">
+      <c r="C8" s="22"/>
+      <c r="D8" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7" t="s">
+      <c r="F8" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="22"/>
+      <c r="H8" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="22"/>
+      <c r="J8" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="L8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="11"/>
-      <c r="N8" s="9" t="s">
+      <c r="L8" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="O8" s="14" t="s">
+      <c r="O8" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="7" t="s">
+      <c r="Q8" s="22"/>
+      <c r="R8" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="S8" s="11" t="s">
+      <c r="S8" s="22" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="7" t="s">
+      <c r="D9" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="22"/>
+      <c r="F9" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="22"/>
+      <c r="H9" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="22"/>
+      <c r="J9" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="22"/>
+      <c r="L9" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="Q9" s="11" t="s">
+      <c r="Q9" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="R9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="S9" s="11"/>
-    </row>
-    <row r="10" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="R9" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="S9" s="22"/>
+    </row>
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B10" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="7" t="s">
+      <c r="D10" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="F10" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="7" t="s">
+      <c r="G10" s="23"/>
+      <c r="H10" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="23"/>
+      <c r="J10" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="K10" s="23"/>
+      <c r="L10" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="P10" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="Q10" s="13" t="s">
+      <c r="Q10" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="R10" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="S10" s="12"/>
-    </row>
-    <row r="11" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
+      <c r="S10" s="23"/>
+    </row>
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B11" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="7" t="s">
+      <c r="D11" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="19"/>
+      <c r="F11" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="7" t="s">
+      <c r="H11" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="19"/>
+      <c r="J11" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="O11" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="P11" s="9" t="s">
+      <c r="P11" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="Q11" s="10" t="s">
+      <c r="Q11" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="R11" s="7" t="s">
+      <c r="R11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="S11" s="8" t="s">
+      <c r="S11" s="19" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="9" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B12" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="9" t="s">
+      <c r="E12" s="22"/>
+      <c r="F12" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7" t="s">
+      <c r="H12" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="22"/>
+      <c r="J12" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="M12" s="14" t="s">
+      <c r="M12" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="P12" s="9" t="s">
+      <c r="P12" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="Q12" s="14" t="s">
+      <c r="Q12" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="R12" s="7" t="s">
+      <c r="R12" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="S12" s="11" t="s">
+      <c r="S12" s="22" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B13" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="7" t="s">
+      <c r="C13" s="22"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="7" t="s">
+      <c r="J13" s="18"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="P13" s="7" t="s">
+      <c r="P13" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="Q13" s="11" t="s">
+      <c r="Q13" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="R13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="S13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="9" t="s">
+      <c r="R13" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="S13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B14" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="7" t="s">
+      <c r="D14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="7" t="s">
+      <c r="K14" s="23"/>
+      <c r="L14" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="9" t="s">
+      <c r="M14" s="23"/>
+      <c r="N14" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="O14" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="P14" s="9" t="s">
+      <c r="P14" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="S14" s="12"/>
-    </row>
-    <row r="15" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7" t="s">
+      <c r="Q14" s="24"/>
+      <c r="R14" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="S14" s="23"/>
+    </row>
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B15" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="7" t="s">
+      <c r="D15" s="18"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="L15" s="7" t="s">
+      <c r="L15" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="M15" s="8" t="s">
+      <c r="M15" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="N15" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="O15" s="8" t="s">
+      <c r="O15" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="P15" s="9" t="s">
+      <c r="P15" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="S15" s="8"/>
-    </row>
-    <row r="16" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="7" t="s">
+      <c r="Q15" s="21"/>
+      <c r="R15" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="S15" s="19"/>
+    </row>
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B16" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K16" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="L16" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="M16" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="N16" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="14" t="s">
+      <c r="O16" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="P16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="S16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
+      <c r="P16" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="S16" s="22"/>
+    </row>
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B17" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="7" t="s">
+      <c r="C17" s="22"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="J17" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M17" s="11"/>
-      <c r="N17" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="S17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="7" t="s">
+      <c r="J17" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="22"/>
+      <c r="L17" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="O17" s="22"/>
+      <c r="P17" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="S17" s="22"/>
+    </row>
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+      <c r="B18" s="18"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="J18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K18" s="12"/>
-      <c r="L18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18" s="12"/>
-      <c r="N18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="O18" s="12"/>
-      <c r="P18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="7" t="s">
+      <c r="J18" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="K18" s="23"/>
+      <c r="L18" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="23"/>
+      <c r="N18" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="O18" s="23"/>
+      <c r="P18" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="S18" s="12"/>
+      <c r="S18" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6056,7 +6100,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="67" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/잦은 뱃노리.xlsx
+++ b/sheets/민요/검수/잦은 뱃노리.xlsx
@@ -5327,23 +5327,23 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="16" width="6"/>
   </cols>
   <sheetData>
